--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R7cab61eedba84708"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="serie_mensal" sheetId="2" r:id="R838686fbc6f84a11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumo_mercados" sheetId="3" r:id="Rb358e22c279749be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sazonalidade" sheetId="4" r:id="Ra7e759205adf4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="picos" sheetId="5" r:id="R25416d9974d0495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="geo_2026" sheetId="6" r:id="R6b5e561e3243454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dashboard_data" sheetId="7" r:id="R2f138f58e673468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="Rc3e9153f59164a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="serie_mensal" sheetId="2" r:id="R0b78326e6a114121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumo_mercados" sheetId="3" r:id="R1ddea3f8c868425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sazonalidade" sheetId="4" r:id="R5d5ece3ae9c14d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="picos" sheetId="5" r:id="Rdd842fba72b44c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="geo_2026" sheetId="6" r:id="Rb5ec37dbce3a4031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dashboard_data" sheetId="7" r:id="Rd8589debb39a495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="geo_historico" sheetId="8" r:id="Rd962f7a0f1cf4088"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,7 +51,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -67,6 +68,11 @@
         <x:fgColor rgb="FFB84E00"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC95B13"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -75,7 +81,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -118,6 +124,9 @@
     <x:xf numFmtId="204" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="205" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -263,7 +272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcec93e237ea5479e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R526b4583ebe7424f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -367,6 +376,20 @@
     <x:tableColumn id="6" name="volatilidade"/>
     <x:tableColumn id="7" name="melhor_mes_sazonal"/>
     <x:tableColumn id="8" name="indice_melhor_mes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="GeoHistorico" displayName="GeoHistorico" ref="A1:F251" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="data_snapshot"/>
+    <x:tableColumn id="2" name="ano"/>
+    <x:tableColumn id="3" name="pais"/>
+    <x:tableColumn id="4" name="indice_trends_num"/>
+    <x:tableColumn id="5" name="indice_trends_exibicao"/>
+    <x:tableColumn id="6" name="termo_google_trends"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -7495,7 +7518,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330126649a464336"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R001887df17804ed7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7887,7 +7910,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra28311afda0843d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5b1b681fc0f4777"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8323,7 +8346,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0daf018fe15540c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R336342bc58774795"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9287,7 +9310,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00e6719dd5394185"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a7c805af02e4610"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12713,7 +12736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a8fd39ed9b64519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R243526c5ce5744a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13000,9 +13023,4189 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb345cf5d955c43c3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf16f3c2fe9264fbf"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc89a6989a53d4e24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec4a9a6b74d4836"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>data_snapshot</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>ano</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>pais</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>indice_trends_num</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>indice_trends_exibicao</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>termo_google_trends</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Chile</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Uruguai</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Argentina</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Paraguai</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Costa Rica</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Panamá</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Peru</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Colômbia</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Portugal</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Equador</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Porto Rico</x:v>
+      </x:c>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Bolívia</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Suíça</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Espanha</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Guatemala</x:v>
+      </x:c>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>México</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Irlanda</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B20" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>República Dominicana</x:v>
+      </x:c>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>França</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Áustria</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Noruega</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Hungria</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Canadá</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Itália</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Alemanha</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Reino Unido</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Países Baixos</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Santa Helena</x:v>
+      </x:c>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Sérvia</x:v>
+      </x:c>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Estados Unidos</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Bélgica</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Tchéquia</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Venezuela</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Singapura</x:v>
+      </x:c>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Suécia</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Israel</x:v>
+      </x:c>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Austrália</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>África do Sul</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Nova Zelândia</x:v>
+      </x:c>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
+      <x:c r="F41" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B42" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Dinamarca</x:v>
+      </x:c>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B43" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Marrocos</x:v>
+      </x:c>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B44" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Romênia</x:v>
+      </x:c>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B45" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Polônia</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>&lt;1</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B46" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Grécia</x:v>
+      </x:c>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B47" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Coreia do Sul</x:v>
+      </x:c>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B48" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Taiwan</x:v>
+      </x:c>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B49" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Turquia</x:v>
+      </x:c>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B50" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Japão</x:v>
+      </x:c>
+      <x:c r="D50" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>&lt;1</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B51" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>Filipinas</x:v>
+      </x:c>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B52" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>Rússia</x:v>
+      </x:c>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B53" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>Índia</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>&lt;1</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B54" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Indonésia</x:v>
+      </x:c>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B55" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Malásia</x:v>
+      </x:c>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B56" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>Vietnã</x:v>
+      </x:c>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B57" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Tailândia</x:v>
+      </x:c>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B58" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>Líbano</x:v>
+      </x:c>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B59" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Zimbábue</x:v>
+      </x:c>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B60" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>Ilhas Cayman</x:v>
+      </x:c>
+      <x:c r="D60"/>
+      <x:c r="E60"/>
+      <x:c r="F60" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B61" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>Ilha Christmas</x:v>
+      </x:c>
+      <x:c r="D61"/>
+      <x:c r="E61"/>
+      <x:c r="F61" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B62" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>Djibuti</x:v>
+      </x:c>
+      <x:c r="D62"/>
+      <x:c r="E62"/>
+      <x:c r="F62" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B63" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>Dominica</x:v>
+      </x:c>
+      <x:c r="D63"/>
+      <x:c r="E63"/>
+      <x:c r="F63" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B64" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>Curaçao</x:v>
+      </x:c>
+      <x:c r="D64"/>
+      <x:c r="E64"/>
+      <x:c r="F64" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B65" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Cuba</x:v>
+      </x:c>
+      <x:c r="D65"/>
+      <x:c r="E65"/>
+      <x:c r="F65" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B66" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Argélia</x:v>
+      </x:c>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B67" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Cabo Verde</x:v>
+      </x:c>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B68" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Egito</x:v>
+      </x:c>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B69" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>Eritreia</x:v>
+      </x:c>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B70" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>Saara Ocidental</x:v>
+      </x:c>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B71" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Comores</x:v>
+      </x:c>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B72" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Estônia</x:v>
+      </x:c>
+      <x:c r="D72"/>
+      <x:c r="E72"/>
+      <x:c r="F72" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B73" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Etiópia</x:v>
+      </x:c>
+      <x:c r="D73"/>
+      <x:c r="E73"/>
+      <x:c r="F73" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B74" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>Finlândia</x:v>
+      </x:c>
+      <x:c r="D74"/>
+      <x:c r="E74"/>
+      <x:c r="F74" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B75" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Fiji</x:v>
+      </x:c>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B76" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Ilhas Malvinas (Ilhas Falkland)</x:v>
+      </x:c>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B77" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Ilhas Cook</x:v>
+      </x:c>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B78" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Ilhas Faroé</x:v>
+      </x:c>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B79" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Micronésia</x:v>
+      </x:c>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B80" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Gabão</x:v>
+      </x:c>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B81" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>República do Congo</x:v>
+      </x:c>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B82" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Geórgia</x:v>
+      </x:c>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B83" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Guernsey</x:v>
+      </x:c>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B84" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>Gana</x:v>
+      </x:c>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B85" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B86" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Guiné</x:v>
+      </x:c>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B87" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>Guadalupe</x:v>
+      </x:c>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B88" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Gâmbia</x:v>
+      </x:c>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B89" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Guiné-Bissau</x:v>
+      </x:c>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B90" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Guiné Equatorial</x:v>
+      </x:c>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B91" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Congo - Kinshasa</x:v>
+      </x:c>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B92" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Granada</x:v>
+      </x:c>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B93" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Groenlândia</x:v>
+      </x:c>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B94" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Camarões</x:v>
+      </x:c>
+      <x:c r="D94"/>
+      <x:c r="E94"/>
+      <x:c r="F94" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B95" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Guiana Francesa</x:v>
+      </x:c>
+      <x:c r="D95"/>
+      <x:c r="E95"/>
+      <x:c r="F95" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B96" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Guam</x:v>
+      </x:c>
+      <x:c r="D96"/>
+      <x:c r="E96"/>
+      <x:c r="F96" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B97" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Guiana</x:v>
+      </x:c>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
+      <x:c r="F97" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B98" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Hong Kong</x:v>
+      </x:c>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B99" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Ilhas Heard e McDonald</x:v>
+      </x:c>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B100" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Honduras</x:v>
+      </x:c>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Croácia</x:v>
+      </x:c>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B102" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Haiti</x:v>
+      </x:c>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B103" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Costa do Marfim</x:v>
+      </x:c>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B104" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B105" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Ilha de Man</x:v>
+      </x:c>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B106" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>Ilhas Cocos (Keeling)</x:v>
+      </x:c>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B107" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>Território Britânico do Oceano Índico</x:v>
+      </x:c>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B108" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>República Centro-Africana</x:v>
+      </x:c>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B109" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>Irã</x:v>
+      </x:c>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B110" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>Iraque</x:v>
+      </x:c>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B111" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>Islândia</x:v>
+      </x:c>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B112" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>Botsuana</x:v>
+      </x:c>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B113" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>Ilha Bouvet</x:v>
+      </x:c>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B114" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>Jamaica</x:v>
+      </x:c>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B115" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>Jersey</x:v>
+      </x:c>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B116" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>Jordânia</x:v>
+      </x:c>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B117" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>Butão</x:v>
+      </x:c>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B118" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>Cazaquistão</x:v>
+      </x:c>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B119" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>Quênia</x:v>
+      </x:c>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
+      <x:c r="F119" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B120" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>Quirguistão</x:v>
+      </x:c>
+      <x:c r="D120"/>
+      <x:c r="E120"/>
+      <x:c r="F120" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B121" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>Camboja</x:v>
+      </x:c>
+      <x:c r="D121"/>
+      <x:c r="E121"/>
+      <x:c r="F121" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B122" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>Quiribati</x:v>
+      </x:c>
+      <x:c r="D122"/>
+      <x:c r="E122"/>
+      <x:c r="F122" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B123" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>São Cristóvão e Névis</x:v>
+      </x:c>
+      <x:c r="D123"/>
+      <x:c r="E123"/>
+      <x:c r="F123" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B124" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>Brunei</x:v>
+      </x:c>
+      <x:c r="D124"/>
+      <x:c r="E124"/>
+      <x:c r="F124" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B125" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>Kuwait</x:v>
+      </x:c>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+      <x:c r="F125" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B126" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>Laos</x:v>
+      </x:c>
+      <x:c r="D126"/>
+      <x:c r="E126"/>
+      <x:c r="F126" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B127" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>Aruba</x:v>
+      </x:c>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B128" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>Angola</x:v>
+      </x:c>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B129" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>Líbia</x:v>
+      </x:c>
+      <x:c r="D129"/>
+      <x:c r="E129"/>
+      <x:c r="F129" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B130" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>Santa Lúcia</x:v>
+      </x:c>
+      <x:c r="D130"/>
+      <x:c r="E130"/>
+      <x:c r="F130" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B131" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>Liechtenstein</x:v>
+      </x:c>
+      <x:c r="D131"/>
+      <x:c r="E131"/>
+      <x:c r="F131" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B132" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>Sri Lanka</x:v>
+      </x:c>
+      <x:c r="D132"/>
+      <x:c r="E132"/>
+      <x:c r="F132" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B133" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>Lesoto</x:v>
+      </x:c>
+      <x:c r="D133"/>
+      <x:c r="E133"/>
+      <x:c r="F133" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B134" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>Lituânia</x:v>
+      </x:c>
+      <x:c r="D134"/>
+      <x:c r="E134"/>
+      <x:c r="F134" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B135" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>Luxemburgo</x:v>
+      </x:c>
+      <x:c r="D135"/>
+      <x:c r="E135"/>
+      <x:c r="F135" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B136" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>Letônia</x:v>
+      </x:c>
+      <x:c r="D136"/>
+      <x:c r="E136"/>
+      <x:c r="F136" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B137" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>Macau</x:v>
+      </x:c>
+      <x:c r="D137"/>
+      <x:c r="E137"/>
+      <x:c r="F137" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B138" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>São Martinho</x:v>
+      </x:c>
+      <x:c r="D138"/>
+      <x:c r="E138"/>
+      <x:c r="F138" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B139" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>Barbados</x:v>
+      </x:c>
+      <x:c r="D139"/>
+      <x:c r="E139"/>
+      <x:c r="F139" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B140" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>Mônaco</x:v>
+      </x:c>
+      <x:c r="D140"/>
+      <x:c r="E140"/>
+      <x:c r="F140" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B141" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>Moldávia</x:v>
+      </x:c>
+      <x:c r="D141"/>
+      <x:c r="E141"/>
+      <x:c r="F141" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B142" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>Madagascar</x:v>
+      </x:c>
+      <x:c r="D142"/>
+      <x:c r="E142"/>
+      <x:c r="F142" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B143" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>Maldivas</x:v>
+      </x:c>
+      <x:c r="D143"/>
+      <x:c r="E143"/>
+      <x:c r="F143" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B144" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>Bermudas</x:v>
+      </x:c>
+      <x:c r="D144"/>
+      <x:c r="E144"/>
+      <x:c r="F144" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B145" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>Ilhas Marshall</x:v>
+      </x:c>
+      <x:c r="D145"/>
+      <x:c r="E145"/>
+      <x:c r="F145" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B146" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>Macedônia do Norte</x:v>
+      </x:c>
+      <x:c r="D146"/>
+      <x:c r="E146"/>
+      <x:c r="F146" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B147" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>Mali</x:v>
+      </x:c>
+      <x:c r="D147"/>
+      <x:c r="E147"/>
+      <x:c r="F147" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B148" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>Malta</x:v>
+      </x:c>
+      <x:c r="D148"/>
+      <x:c r="E148"/>
+      <x:c r="F148" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B149" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>Mianmar (Birmânia)</x:v>
+      </x:c>
+      <x:c r="D149"/>
+      <x:c r="E149"/>
+      <x:c r="F149" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B150" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>Montenegro</x:v>
+      </x:c>
+      <x:c r="D150"/>
+      <x:c r="E150"/>
+      <x:c r="F150" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B151" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>Mongólia</x:v>
+      </x:c>
+      <x:c r="D151"/>
+      <x:c r="E151"/>
+      <x:c r="F151" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B152" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>Ilhas Marianas do Norte</x:v>
+      </x:c>
+      <x:c r="D152"/>
+      <x:c r="E152"/>
+      <x:c r="F152" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B153" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>Moçambique</x:v>
+      </x:c>
+      <x:c r="D153"/>
+      <x:c r="E153"/>
+      <x:c r="F153" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B154" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>Mauritânia</x:v>
+      </x:c>
+      <x:c r="D154"/>
+      <x:c r="E154"/>
+      <x:c r="F154" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B155" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>Chipre</x:v>
+      </x:c>
+      <x:c r="D155"/>
+      <x:c r="E155"/>
+      <x:c r="F155" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B156" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>Martinica</x:v>
+      </x:c>
+      <x:c r="D156"/>
+      <x:c r="E156"/>
+      <x:c r="F156" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B157" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>Maurício</x:v>
+      </x:c>
+      <x:c r="D157"/>
+      <x:c r="E157"/>
+      <x:c r="F157" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B158" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>Malaui</x:v>
+      </x:c>
+      <x:c r="D158"/>
+      <x:c r="E158"/>
+      <x:c r="F158" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B159" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>Belize</x:v>
+      </x:c>
+      <x:c r="D159"/>
+      <x:c r="E159"/>
+      <x:c r="F159" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B160" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>Mayotte</x:v>
+      </x:c>
+      <x:c r="D160"/>
+      <x:c r="E160"/>
+      <x:c r="F160" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B161" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>Namíbia</x:v>
+      </x:c>
+      <x:c r="D161"/>
+      <x:c r="E161"/>
+      <x:c r="F161" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B162" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>Nova Caledônia</x:v>
+      </x:c>
+      <x:c r="D162"/>
+      <x:c r="E162"/>
+      <x:c r="F162" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B163" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>Níger</x:v>
+      </x:c>
+      <x:c r="D163"/>
+      <x:c r="E163"/>
+      <x:c r="F163" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B164" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>Ilha Norfolk</x:v>
+      </x:c>
+      <x:c r="D164"/>
+      <x:c r="E164"/>
+      <x:c r="F164" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B165" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>Nigéria</x:v>
+      </x:c>
+      <x:c r="D165"/>
+      <x:c r="E165"/>
+      <x:c r="F165" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B166" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>Nicarágua</x:v>
+      </x:c>
+      <x:c r="D166"/>
+      <x:c r="E166"/>
+      <x:c r="F166" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B167" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>Niue</x:v>
+      </x:c>
+      <x:c r="D167"/>
+      <x:c r="E167"/>
+      <x:c r="F167" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B168" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>Bielorrússia</x:v>
+      </x:c>
+      <x:c r="D168"/>
+      <x:c r="E168"/>
+      <x:c r="F168" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B169" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>São Bartolomeu</x:v>
+      </x:c>
+      <x:c r="D169"/>
+      <x:c r="E169"/>
+      <x:c r="F169" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B170" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>Nepal</x:v>
+      </x:c>
+      <x:c r="D170"/>
+      <x:c r="E170"/>
+      <x:c r="F170" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B171" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>Nauru</x:v>
+      </x:c>
+      <x:c r="D171"/>
+      <x:c r="E171"/>
+      <x:c r="F171" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B172" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>Bósnia e Herzegovina</x:v>
+      </x:c>
+      <x:c r="D172"/>
+      <x:c r="E172"/>
+      <x:c r="F172" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B173" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>Omã</x:v>
+      </x:c>
+      <x:c r="D173"/>
+      <x:c r="E173"/>
+      <x:c r="F173" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B174" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>Paquistão</x:v>
+      </x:c>
+      <x:c r="D174"/>
+      <x:c r="E174"/>
+      <x:c r="F174" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B175" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>Bahamas</x:v>
+      </x:c>
+      <x:c r="D175"/>
+      <x:c r="E175"/>
+      <x:c r="F175" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>Ilhas Pitcairn</x:v>
+      </x:c>
+      <x:c r="D176"/>
+      <x:c r="E176"/>
+      <x:c r="F176" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B177" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>Barein</x:v>
+      </x:c>
+      <x:c r="D177"/>
+      <x:c r="E177"/>
+      <x:c r="F177" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B178" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>Bulgária</x:v>
+      </x:c>
+      <x:c r="D178"/>
+      <x:c r="E178"/>
+      <x:c r="F178" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B179" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>Palau</x:v>
+      </x:c>
+      <x:c r="D179"/>
+      <x:c r="E179"/>
+      <x:c r="F179" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B180" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>Papua-Nova Guiné</x:v>
+      </x:c>
+      <x:c r="D180"/>
+      <x:c r="E180"/>
+      <x:c r="F180" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B181" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>Bangladesh</x:v>
+      </x:c>
+      <x:c r="D181"/>
+      <x:c r="E181"/>
+      <x:c r="F181" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B182" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>Burquina Faso</x:v>
+      </x:c>
+      <x:c r="D182"/>
+      <x:c r="E182"/>
+      <x:c r="F182" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B183" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>Coreia do Norte</x:v>
+      </x:c>
+      <x:c r="D183"/>
+      <x:c r="E183"/>
+      <x:c r="F183" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B184" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>Países Baixos Caribenhos</x:v>
+      </x:c>
+      <x:c r="D184"/>
+      <x:c r="E184"/>
+      <x:c r="F184" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B185" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>Benin</x:v>
+      </x:c>
+      <x:c r="D185"/>
+      <x:c r="E185"/>
+      <x:c r="F185" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B186" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>Palestina</x:v>
+      </x:c>
+      <x:c r="D186"/>
+      <x:c r="E186"/>
+      <x:c r="F186" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B187" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>Polinésia Francesa</x:v>
+      </x:c>
+      <x:c r="D187"/>
+      <x:c r="E187"/>
+      <x:c r="F187" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B188" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>Catar</x:v>
+      </x:c>
+      <x:c r="D188"/>
+      <x:c r="E188"/>
+      <x:c r="F188" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B189" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>Reunião</x:v>
+      </x:c>
+      <x:c r="D189"/>
+      <x:c r="E189"/>
+      <x:c r="F189" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B190" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>Burundi</x:v>
+      </x:c>
+      <x:c r="D190"/>
+      <x:c r="E190"/>
+      <x:c r="F190" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B191" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>Azerbaijão</x:v>
+      </x:c>
+      <x:c r="D191"/>
+      <x:c r="E191"/>
+      <x:c r="F191" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B192" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>Ruanda</x:v>
+      </x:c>
+      <x:c r="D192"/>
+      <x:c r="E192"/>
+      <x:c r="F192" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B193" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>Arábia Saudita</x:v>
+      </x:c>
+      <x:c r="D193"/>
+      <x:c r="E193"/>
+      <x:c r="F193" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B194" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>Sudão</x:v>
+      </x:c>
+      <x:c r="D194"/>
+      <x:c r="E194"/>
+      <x:c r="F194" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B195" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>Senegal</x:v>
+      </x:c>
+      <x:c r="D195"/>
+      <x:c r="E195"/>
+      <x:c r="F195" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B196" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>Antígua e Barbuda</x:v>
+      </x:c>
+      <x:c r="D196"/>
+      <x:c r="E196"/>
+      <x:c r="F196" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B197" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>Ilhas Geórgia do Sul e Sandwich do Sul</x:v>
+      </x:c>
+      <x:c r="D197"/>
+      <x:c r="E197"/>
+      <x:c r="F197" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B198" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>Territórios Franceses do Sul</x:v>
+      </x:c>
+      <x:c r="D198"/>
+      <x:c r="E198"/>
+      <x:c r="F198" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B199" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>Svalbard e Jan Mayen</x:v>
+      </x:c>
+      <x:c r="D199"/>
+      <x:c r="E199"/>
+      <x:c r="F199" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B200" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>Ilhas Salomão</x:v>
+      </x:c>
+      <x:c r="D200"/>
+      <x:c r="E200"/>
+      <x:c r="F200" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B201" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>Serra Leoa</x:v>
+      </x:c>
+      <x:c r="D201"/>
+      <x:c r="E201"/>
+      <x:c r="F201" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B202" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>El Salvador</x:v>
+      </x:c>
+      <x:c r="D202"/>
+      <x:c r="E202"/>
+      <x:c r="F202" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B203" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>San Marino</x:v>
+      </x:c>
+      <x:c r="D203"/>
+      <x:c r="E203"/>
+      <x:c r="F203" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B204" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>Somália</x:v>
+      </x:c>
+      <x:c r="D204"/>
+      <x:c r="E204"/>
+      <x:c r="F204" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B205" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>São Pedro e Miquelão</x:v>
+      </x:c>
+      <x:c r="D205"/>
+      <x:c r="E205"/>
+      <x:c r="F205" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B206" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>Antártida</x:v>
+      </x:c>
+      <x:c r="D206"/>
+      <x:c r="E206"/>
+      <x:c r="F206" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B207" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>Sudão do Sul</x:v>
+      </x:c>
+      <x:c r="D207"/>
+      <x:c r="E207"/>
+      <x:c r="F207" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B208" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>São Tomé e Príncipe</x:v>
+      </x:c>
+      <x:c r="D208"/>
+      <x:c r="E208"/>
+      <x:c r="F208" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B209" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>Suriname</x:v>
+      </x:c>
+      <x:c r="D209"/>
+      <x:c r="E209"/>
+      <x:c r="F209" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B210" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>Eslováquia</x:v>
+      </x:c>
+      <x:c r="D210"/>
+      <x:c r="E210"/>
+      <x:c r="F210" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B211" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>Eslovênia</x:v>
+      </x:c>
+      <x:c r="D211"/>
+      <x:c r="E211"/>
+      <x:c r="F211" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B212" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>Samoa Americana</x:v>
+      </x:c>
+      <x:c r="D212"/>
+      <x:c r="E212"/>
+      <x:c r="F212" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B213" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>Essuatíni</x:v>
+      </x:c>
+      <x:c r="D213"/>
+      <x:c r="E213"/>
+      <x:c r="F213" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B214" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>Sint Maarten</x:v>
+      </x:c>
+      <x:c r="D214"/>
+      <x:c r="E214"/>
+      <x:c r="F214" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B215" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>Seicheles</x:v>
+      </x:c>
+      <x:c r="D215"/>
+      <x:c r="E215"/>
+      <x:c r="F215" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B216" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>Síria</x:v>
+      </x:c>
+      <x:c r="D216"/>
+      <x:c r="E216"/>
+      <x:c r="F216" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B217" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>Ilhas Turcas e Caicos</x:v>
+      </x:c>
+      <x:c r="D217"/>
+      <x:c r="E217"/>
+      <x:c r="F217" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B218" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>Chade</x:v>
+      </x:c>
+      <x:c r="D218"/>
+      <x:c r="E218"/>
+      <x:c r="F218" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B219" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>Togo</x:v>
+      </x:c>
+      <x:c r="D219"/>
+      <x:c r="E219"/>
+      <x:c r="F219" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B220" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>Armênia</x:v>
+      </x:c>
+      <x:c r="D220"/>
+      <x:c r="E220"/>
+      <x:c r="F220" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B221" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>Tadjiquistão</x:v>
+      </x:c>
+      <x:c r="D221"/>
+      <x:c r="E221"/>
+      <x:c r="F221" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B222" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>Tokelau</x:v>
+      </x:c>
+      <x:c r="D222"/>
+      <x:c r="E222"/>
+      <x:c r="F222" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B223" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>Turcomenistão</x:v>
+      </x:c>
+      <x:c r="D223"/>
+      <x:c r="E223"/>
+      <x:c r="F223" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B224" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>Timor-Leste</x:v>
+      </x:c>
+      <x:c r="D224"/>
+      <x:c r="E224"/>
+      <x:c r="F224" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B225" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>Tonga</x:v>
+      </x:c>
+      <x:c r="D225"/>
+      <x:c r="E225"/>
+      <x:c r="F225" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B226" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>Trinidad e Tobago</x:v>
+      </x:c>
+      <x:c r="D226"/>
+      <x:c r="E226"/>
+      <x:c r="F226" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B227" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>Tunísia</x:v>
+      </x:c>
+      <x:c r="D227"/>
+      <x:c r="E227"/>
+      <x:c r="F227" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B228" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>Emirados Árabes Unidos</x:v>
+      </x:c>
+      <x:c r="D228"/>
+      <x:c r="E228"/>
+      <x:c r="F228" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B229" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>Tuvalu</x:v>
+      </x:c>
+      <x:c r="D229"/>
+      <x:c r="E229"/>
+      <x:c r="F229" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B230" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>Andorra</x:v>
+      </x:c>
+      <x:c r="D230"/>
+      <x:c r="E230"/>
+      <x:c r="F230" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B231" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>Tanzânia</x:v>
+      </x:c>
+      <x:c r="D231"/>
+      <x:c r="E231"/>
+      <x:c r="F231" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B232" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>Uganda</x:v>
+      </x:c>
+      <x:c r="D232"/>
+      <x:c r="E232"/>
+      <x:c r="F232" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B233" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>Ucrânia</x:v>
+      </x:c>
+      <x:c r="D233"/>
+      <x:c r="E233"/>
+      <x:c r="F233" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B234" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>Ilhas Menores Distantes dos EUA</x:v>
+      </x:c>
+      <x:c r="D234"/>
+      <x:c r="E234"/>
+      <x:c r="F234" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B235" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>Albânia</x:v>
+      </x:c>
+      <x:c r="D235"/>
+      <x:c r="E235"/>
+      <x:c r="F235" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B236" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>Ilhas Aland</x:v>
+      </x:c>
+      <x:c r="D236"/>
+      <x:c r="E236"/>
+      <x:c r="F236" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B237" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>Uzbequistão</x:v>
+      </x:c>
+      <x:c r="D237"/>
+      <x:c r="E237"/>
+      <x:c r="F237" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B238" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>Cidade do Vaticano</x:v>
+      </x:c>
+      <x:c r="D238"/>
+      <x:c r="E238"/>
+      <x:c r="F238" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B239" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>São Vicente e Granadinas</x:v>
+      </x:c>
+      <x:c r="D239"/>
+      <x:c r="E239"/>
+      <x:c r="F239" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B240" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>Anguila</x:v>
+      </x:c>
+      <x:c r="D240"/>
+      <x:c r="E240"/>
+      <x:c r="F240" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B241" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>Ilhas Virgens Britânicas</x:v>
+      </x:c>
+      <x:c r="D241"/>
+      <x:c r="E241"/>
+      <x:c r="F241" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B242" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>Ilhas Virgens Americanas</x:v>
+      </x:c>
+      <x:c r="D242"/>
+      <x:c r="E242"/>
+      <x:c r="F242" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B243" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>Afeganistão</x:v>
+      </x:c>
+      <x:c r="D243"/>
+      <x:c r="E243"/>
+      <x:c r="F243" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B244" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>Vanuatu</x:v>
+      </x:c>
+      <x:c r="D244"/>
+      <x:c r="E244"/>
+      <x:c r="F244" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B245" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C245" t="str">
+        <x:v>Wallis e Futuna</x:v>
+      </x:c>
+      <x:c r="D245"/>
+      <x:c r="E245"/>
+      <x:c r="F245" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B246" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C246" t="str">
+        <x:v>Samoa</x:v>
+      </x:c>
+      <x:c r="D246"/>
+      <x:c r="E246"/>
+      <x:c r="F246" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B247" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C247" t="str">
+        <x:v>Kosovo</x:v>
+      </x:c>
+      <x:c r="D247"/>
+      <x:c r="E247"/>
+      <x:c r="F247" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B248" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C248" t="str">
+        <x:v>Iêmen</x:v>
+      </x:c>
+      <x:c r="D248"/>
+      <x:c r="E248"/>
+      <x:c r="F248" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B249" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C249" t="str">
+        <x:v>Libéria</x:v>
+      </x:c>
+      <x:c r="D249"/>
+      <x:c r="E249"/>
+      <x:c r="F249" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B250" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C250" t="str">
+        <x:v>Zâmbia</x:v>
+      </x:c>
+      <x:c r="D250"/>
+      <x:c r="E250"/>
+      <x:c r="F250" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="18" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="B251" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C251" t="str">
+        <x:v>Montserrat</x:v>
+      </x:c>
+      <x:c r="D251"/>
+      <x:c r="E251"/>
+      <x:c r="F251" t="str">
+        <x:v>Pão de Açúcar</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12fe579baf44d59"/>
   </x:tableParts>
 </x:worksheet>
 </file>